--- a/GENERADOR PLANILLA/docentes.xlsx
+++ b/GENERADOR PLANILLA/docentes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodri\Escritorio\PROGRAMA CEID\GENERADOR PLANILLA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodri\Escritorio\CEID-Generator\GENERADOR PLANILLA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED77EC8B-B8BD-4CE5-A3DA-589749160582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2479EAEA-B0F5-4941-8BBB-C1274EE1E99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="556">
   <si>
     <t>N°</t>
   </si>
@@ -130,9 +130,6 @@
     <t>Alves Vieira, Vera Helena</t>
   </si>
   <si>
-    <t>970 657 628</t>
-  </si>
-  <si>
     <t>Av. Costanera 2810- Dpt. 401, San Miguel</t>
   </si>
   <si>
@@ -1153,9 +1150,6 @@
     <t>docenteceid160.flch@unmsm.edu.pe</t>
   </si>
   <si>
-    <t>959 222 749</t>
-  </si>
-  <si>
     <t>Asoc. Parc. Cieneguilla- Av. Nueva Toledo- Mz.T- Lt.7A, Cieneguilla</t>
   </si>
   <si>
@@ -1168,9 +1162,6 @@
     <t>Quispe Zorrilla, Eva Luz</t>
   </si>
   <si>
-    <t>928 085 619</t>
-  </si>
-  <si>
     <t>A.H. Cruz de Motupe- Grupo 4- Av. Central- Mz. B- Lt. 011, SJL</t>
   </si>
   <si>
@@ -1300,9 +1291,6 @@
     <t>Sebastiani Carranza, Gloria Clementina</t>
   </si>
   <si>
-    <t>969 338 549</t>
-  </si>
-  <si>
     <t>Unidad Vecinal N° 3 – block 53-D - 2, Lima</t>
   </si>
   <si>
@@ -1595,6 +1583,114 @@
   </si>
   <si>
     <t>Quispe Cuadros, XuLi Maria</t>
+  </si>
+  <si>
+    <t>09338087</t>
+  </si>
+  <si>
+    <t>08738041</t>
+  </si>
+  <si>
+    <t>04083732</t>
+  </si>
+  <si>
+    <t>06017324</t>
+  </si>
+  <si>
+    <t>06419008</t>
+  </si>
+  <si>
+    <t>06676094</t>
+  </si>
+  <si>
+    <t>06700013</t>
+  </si>
+  <si>
+    <t>06743423</t>
+  </si>
+  <si>
+    <t>06794007</t>
+  </si>
+  <si>
+    <t>07349193</t>
+  </si>
+  <si>
+    <t>07350311</t>
+  </si>
+  <si>
+    <t>07451650</t>
+  </si>
+  <si>
+    <t>07464127</t>
+  </si>
+  <si>
+    <t>07526164</t>
+  </si>
+  <si>
+    <t>07530344</t>
+  </si>
+  <si>
+    <t>07578484</t>
+  </si>
+  <si>
+    <t>07730879</t>
+  </si>
+  <si>
+    <t>07905708</t>
+  </si>
+  <si>
+    <t>08008610</t>
+  </si>
+  <si>
+    <t>08050454</t>
+  </si>
+  <si>
+    <t>08057228</t>
+  </si>
+  <si>
+    <t>08257531</t>
+  </si>
+  <si>
+    <t>08563743</t>
+  </si>
+  <si>
+    <t>08685671</t>
+  </si>
+  <si>
+    <t>08834548</t>
+  </si>
+  <si>
+    <t>08887336</t>
+  </si>
+  <si>
+    <t>09342352</t>
+  </si>
+  <si>
+    <t>09406568</t>
+  </si>
+  <si>
+    <t>09415139</t>
+  </si>
+  <si>
+    <t>09442016</t>
+  </si>
+  <si>
+    <t>09462707</t>
+  </si>
+  <si>
+    <t>09589024</t>
+  </si>
+  <si>
+    <t>09610698</t>
+  </si>
+  <si>
+    <t>09677923</t>
+  </si>
+  <si>
+    <t>09777112</t>
+  </si>
+  <si>
+    <t>09888411</t>
   </si>
 </sst>
 </file>
@@ -1658,12 +1754,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1976,8 +2075,8 @@
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="75.42578125" bestFit="1" customWidth="1"/>
@@ -2042,7 +2141,7 @@
       <c r="F2" s="1">
         <v>10460255924</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="3">
         <v>46025592</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -2080,7 +2179,7 @@
       <c r="F3" s="1">
         <v>10424766921</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="3">
         <v>42476692</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -2118,7 +2217,7 @@
       <c r="F4" s="1">
         <v>10730465659</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="3">
         <v>73046565</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -2156,7 +2255,7 @@
       <c r="F5" s="1">
         <v>10429394380</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="3">
         <v>42939438</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -2194,23 +2293,23 @@
       <c r="F6" s="1">
         <v>15538262703</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="3">
         <v>53826270</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="1">
+        <v>970657628</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -2218,7 +2317,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
@@ -2232,7 +2331,7 @@
       <c r="F7" s="1">
         <v>10254030321</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="3">
         <v>25403032</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -2242,13 +2341,13 @@
         <v>971181791</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2256,7 +2355,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
@@ -2270,7 +2369,7 @@
       <c r="F8" s="1">
         <v>10335990973</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="3">
         <v>33599097</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -2286,7 +2385,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>13</v>
@@ -2300,7 +2399,7 @@
       <c r="F9" s="1">
         <v>10474046333</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="3">
         <v>47404633</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -2310,13 +2409,13 @@
         <v>934948077</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -2324,7 +2423,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>13</v>
@@ -2338,7 +2437,7 @@
       <c r="F10" s="1">
         <v>10432006552</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="3">
         <v>43200655</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -2348,13 +2447,13 @@
         <v>931588582</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -2362,7 +2461,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>13</v>
@@ -2376,7 +2475,7 @@
       <c r="F11" s="1">
         <v>10256584846</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="3">
         <v>25658484</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -2386,13 +2485,13 @@
         <v>977388884</v>
       </c>
       <c r="J11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -2400,13 +2499,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="E12" s="1">
         <v>40</v>
@@ -2414,8 +2513,8 @@
       <c r="F12" s="1">
         <v>10093380873</v>
       </c>
-      <c r="G12" s="1">
-        <v>9338087</v>
+      <c r="G12" s="3" t="s">
+        <v>520</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>26</v>
@@ -2424,13 +2523,13 @@
         <v>955147260</v>
       </c>
       <c r="J12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2438,7 +2537,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
@@ -2452,7 +2551,7 @@
       <c r="F13" s="1">
         <v>10634204011</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="3">
         <v>63420401</v>
       </c>
       <c r="H13" s="1" t="s">
@@ -2462,13 +2561,13 @@
         <v>968527528</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2476,7 +2575,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>13</v>
@@ -2490,8 +2589,8 @@
       <c r="F14" s="1">
         <v>10087380411</v>
       </c>
-      <c r="G14" s="1">
-        <v>8738041</v>
+      <c r="G14" s="3" t="s">
+        <v>521</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>26</v>
@@ -2500,13 +2599,13 @@
         <v>989104740</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2514,7 +2613,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>13</v>
@@ -2528,8 +2627,8 @@
       <c r="F15" s="1">
         <v>10075261646</v>
       </c>
-      <c r="G15" s="1">
-        <v>7526164</v>
+      <c r="G15" s="3" t="s">
+        <v>533</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -2538,13 +2637,13 @@
         <v>931295320</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2552,13 +2651,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1">
         <v>40</v>
@@ -2566,8 +2665,8 @@
       <c r="F16" s="1">
         <v>10094065688</v>
       </c>
-      <c r="G16" s="1">
-        <v>9406568</v>
+      <c r="G16" s="3" t="s">
+        <v>547</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -2576,13 +2675,13 @@
         <v>998706642</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -2590,7 +2689,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>13</v>
@@ -2604,7 +2703,7 @@
       <c r="F17" s="1">
         <v>10257417421</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="3">
         <v>25741742</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -2614,13 +2713,13 @@
         <v>922569623</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -2628,7 +2727,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>13</v>
@@ -2642,7 +2741,7 @@
       <c r="F18" s="1">
         <v>10154531837</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="3">
         <v>15453183</v>
       </c>
       <c r="H18" s="1" t="s">
@@ -2652,13 +2751,13 @@
         <v>938538761</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -2666,7 +2765,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>13</v>
@@ -2680,7 +2779,7 @@
       <c r="F19" s="1">
         <v>10460174665</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="3">
         <v>46017466</v>
       </c>
       <c r="H19" s="1" t="s">
@@ -2690,13 +2789,13 @@
         <v>986786251</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -2704,7 +2803,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>13</v>
@@ -2718,7 +2817,7 @@
       <c r="F20" s="1">
         <v>15546950040</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="3">
         <v>54695004</v>
       </c>
       <c r="H20" s="1" t="s">
@@ -2728,13 +2827,13 @@
         <v>934890626</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -2742,13 +2841,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="1">
         <v>40</v>
@@ -2756,7 +2855,7 @@
       <c r="F21" s="1">
         <v>10421147103</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="3">
         <v>42114710</v>
       </c>
       <c r="H21" s="1" t="s">
@@ -2766,13 +2865,13 @@
         <v>993243156</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -2780,7 +2879,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>13</v>
@@ -2794,8 +2893,8 @@
       <c r="F22" s="1">
         <v>10074641275</v>
       </c>
-      <c r="G22" s="1">
-        <v>7464127</v>
+      <c r="G22" s="3" t="s">
+        <v>532</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -2804,13 +2903,13 @@
         <v>994788525</v>
       </c>
       <c r="J22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -2818,13 +2917,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" s="1">
         <v>40</v>
@@ -2832,8 +2931,8 @@
       <c r="F23" s="1">
         <v>10067940071</v>
       </c>
-      <c r="G23" s="1">
-        <v>6794007</v>
+      <c r="G23" s="3" t="s">
+        <v>528</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -2842,13 +2941,13 @@
         <v>999928261</v>
       </c>
       <c r="J23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -2856,7 +2955,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>13</v>
@@ -2870,7 +2969,7 @@
       <c r="F24" s="1">
         <v>10750028956</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="3">
         <v>75002895</v>
       </c>
       <c r="H24" s="1" t="s">
@@ -2880,13 +2979,13 @@
         <v>900600638</v>
       </c>
       <c r="J24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -2894,7 +2993,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>13</v>
@@ -2908,7 +3007,7 @@
       <c r="F25" s="1">
         <v>10705547781</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="3">
         <v>70554778</v>
       </c>
       <c r="H25" s="1" t="s">
@@ -2918,13 +3017,13 @@
         <v>950351655</v>
       </c>
       <c r="J25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2932,7 +3031,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -2946,7 +3045,7 @@
       <c r="F26" s="1">
         <v>10462537838</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="3">
         <v>46253783</v>
       </c>
       <c r="H26" s="1" t="s">
@@ -2956,13 +3055,13 @@
         <v>940569042</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2970,7 +3069,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>13</v>
@@ -2984,7 +3083,7 @@
       <c r="F27" s="1">
         <v>10438071631</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="3">
         <v>43807163</v>
       </c>
       <c r="H27" s="1" t="s">
@@ -2994,13 +3093,13 @@
         <v>932424767</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -3008,13 +3107,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -3022,8 +3121,8 @@
       <c r="F28" s="1">
         <v>10080572285</v>
       </c>
-      <c r="G28" s="1">
-        <v>8057228</v>
+      <c r="G28" s="3" t="s">
+        <v>540</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>26</v>
@@ -3038,7 +3137,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>13</v>
@@ -3052,7 +3151,7 @@
       <c r="F29" s="1">
         <v>10422833922</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="3">
         <v>42283392</v>
       </c>
       <c r="H29" s="1" t="s">
@@ -3062,13 +3161,13 @@
         <v>922949352</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -3076,13 +3175,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
@@ -3090,7 +3189,7 @@
       <c r="F30" s="1">
         <v>10400434587</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="3">
         <v>40043458</v>
       </c>
       <c r="H30" s="1" t="s">
@@ -3106,7 +3205,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>13</v>
@@ -3120,8 +3219,8 @@
       <c r="F31" s="1">
         <v>10075303446</v>
       </c>
-      <c r="G31" s="1">
-        <v>7530344</v>
+      <c r="G31" s="3" t="s">
+        <v>534</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>26</v>
@@ -3130,13 +3229,13 @@
         <v>997262896</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -3144,7 +3243,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>13</v>
@@ -3158,8 +3257,8 @@
       <c r="F32" s="1">
         <v>10067434230</v>
       </c>
-      <c r="G32" s="1">
-        <v>6743423</v>
+      <c r="G32" s="3" t="s">
+        <v>527</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -3168,13 +3267,13 @@
         <v>999670291</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -3182,7 +3281,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>20</v>
@@ -3196,7 +3295,7 @@
       <c r="F33" s="1">
         <v>10714903701</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" s="3">
         <v>71490370</v>
       </c>
       <c r="H33" s="1" t="s">
@@ -3206,13 +3305,13 @@
         <v>979665420</v>
       </c>
       <c r="J33" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -3220,7 +3319,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>13</v>
@@ -3234,8 +3333,8 @@
       <c r="F34" s="1">
         <v>10082575311</v>
       </c>
-      <c r="G34" s="1">
-        <v>8257531</v>
+      <c r="G34" s="3" t="s">
+        <v>541</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>26</v>
@@ -3244,13 +3343,13 @@
         <v>999988382</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -3258,7 +3357,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>13</v>
@@ -3272,8 +3371,8 @@
       <c r="F35" s="1">
         <v>10079057083</v>
       </c>
-      <c r="G35" s="1">
-        <v>7905708</v>
+      <c r="G35" s="3" t="s">
+        <v>537</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>15</v>
@@ -3282,13 +3381,13 @@
         <v>993781863</v>
       </c>
       <c r="J35" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -3296,7 +3395,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>13</v>
@@ -3310,7 +3409,7 @@
       <c r="F36" s="1">
         <v>10728670822</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" s="3">
         <v>72867082</v>
       </c>
       <c r="H36" s="1" t="s">
@@ -3320,13 +3419,13 @@
         <v>926688772</v>
       </c>
       <c r="J36" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -3334,13 +3433,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E37" s="1">
         <v>40</v>
@@ -3348,8 +3447,8 @@
       <c r="F37" s="1">
         <v>10094627074</v>
       </c>
-      <c r="G37" s="1">
-        <v>9462707</v>
+      <c r="G37" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>26</v>
@@ -3358,13 +3457,13 @@
         <v>954077587</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -3372,7 +3471,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>13</v>
@@ -3386,7 +3485,7 @@
       <c r="F38" s="1">
         <v>10444447970</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="3">
         <v>44444797</v>
       </c>
       <c r="H38" s="1" t="s">
@@ -3396,13 +3495,13 @@
         <v>997400460</v>
       </c>
       <c r="J38" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -3410,7 +3509,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>20</v>
@@ -3424,7 +3523,7 @@
       <c r="F39" s="1">
         <v>10427243767</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" s="3">
         <v>42724376</v>
       </c>
       <c r="H39" s="1" t="s">
@@ -3434,13 +3533,13 @@
         <v>943102833</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -3448,7 +3547,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>20</v>
@@ -3462,7 +3561,7 @@
       <c r="F40" s="1">
         <v>10409793792</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" s="3">
         <v>40979379</v>
       </c>
       <c r="H40" s="1" t="s">
@@ -3472,13 +3571,13 @@
         <v>991631267</v>
       </c>
       <c r="J40" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -3486,13 +3585,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E41" s="1">
         <v>40</v>
@@ -3500,7 +3599,7 @@
       <c r="F41" s="1">
         <v>10433415367</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" s="3">
         <v>43341536</v>
       </c>
       <c r="H41" s="1" t="s">
@@ -3510,10 +3609,10 @@
         <v>5545999335883</v>
       </c>
       <c r="J41" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="L41" s="1"/>
     </row>
@@ -3522,13 +3621,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E42" s="1">
         <v>40</v>
@@ -3536,7 +3635,7 @@
       <c r="F42" s="1">
         <v>10460117301</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" s="3">
         <v>46011730</v>
       </c>
       <c r="H42" s="1" t="s">
@@ -3546,13 +3645,13 @@
         <v>969792010</v>
       </c>
       <c r="J42" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -3560,7 +3659,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>13</v>
@@ -3574,8 +3673,8 @@
       <c r="F43" s="1">
         <v>10088873365</v>
       </c>
-      <c r="G43" s="1">
-        <v>8887336</v>
+      <c r="G43" s="3" t="s">
+        <v>545</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>26</v>
@@ -3590,7 +3689,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>13</v>
@@ -3604,8 +3703,8 @@
       <c r="F44" s="1">
         <v>10075784843</v>
       </c>
-      <c r="G44" s="1">
-        <v>7578484</v>
+      <c r="G44" s="3" t="s">
+        <v>535</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>26</v>
@@ -3614,13 +3713,13 @@
         <v>935546353</v>
       </c>
       <c r="J44" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -3628,7 +3727,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>20</v>
@@ -3642,7 +3741,7 @@
       <c r="F45" s="1">
         <v>10420335721</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G45" s="3">
         <v>42033572</v>
       </c>
       <c r="H45" s="1" t="s">
@@ -3652,13 +3751,13 @@
         <v>941153492</v>
       </c>
       <c r="J45" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -3666,7 +3765,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>13</v>
@@ -3680,23 +3779,23 @@
       <c r="F46" s="1">
         <v>15553387369</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G46" s="3">
         <v>55338736</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="I46" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="K46" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -3704,7 +3803,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>13</v>
@@ -3718,7 +3817,7 @@
       <c r="F47" s="1">
         <v>15555496998</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G47" s="3">
         <v>55549699</v>
       </c>
       <c r="H47" s="1" t="s">
@@ -3728,13 +3827,13 @@
         <v>986923783</v>
       </c>
       <c r="J47" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -3742,7 +3841,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>13</v>
@@ -3756,7 +3855,7 @@
       <c r="F48" s="1">
         <v>10408742787</v>
       </c>
-      <c r="G48" s="1">
+      <c r="G48" s="3">
         <v>40874278</v>
       </c>
       <c r="H48" s="1" t="s">
@@ -3766,13 +3865,13 @@
         <v>976808890</v>
       </c>
       <c r="J48" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -3780,7 +3879,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>13</v>
@@ -3794,7 +3893,7 @@
       <c r="F49" s="1">
         <v>10704231861</v>
       </c>
-      <c r="G49" s="1">
+      <c r="G49" s="3">
         <v>70423186</v>
       </c>
       <c r="H49" s="1" t="s">
@@ -3804,13 +3903,13 @@
         <v>938874709</v>
       </c>
       <c r="J49" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -3818,13 +3917,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E50" s="1">
         <v>40</v>
@@ -3832,7 +3931,7 @@
       <c r="F50" s="1">
         <v>15610634319</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G50" s="3">
         <v>61063431</v>
       </c>
       <c r="H50" s="1" t="s">
@@ -3848,7 +3947,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>13</v>
@@ -3862,7 +3961,7 @@
       <c r="F51" s="1">
         <v>10413612816</v>
       </c>
-      <c r="G51" s="1">
+      <c r="G51" s="3">
         <v>41361281</v>
       </c>
       <c r="H51" s="1" t="s">
@@ -3872,13 +3971,13 @@
         <v>997950197</v>
       </c>
       <c r="J51" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3886,13 +3985,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E52" s="1">
         <v>40</v>
@@ -3900,7 +3999,7 @@
       <c r="F52" s="1">
         <v>10437708105</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G52" s="3">
         <v>43770810</v>
       </c>
       <c r="H52" s="1" t="s">
@@ -3910,13 +4009,13 @@
         <v>996331358</v>
       </c>
       <c r="J52" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,7 +4023,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>13</v>
@@ -3938,8 +4037,8 @@
       <c r="F53" s="1">
         <v>10094420160</v>
       </c>
-      <c r="G53" s="1">
-        <v>9442016</v>
+      <c r="G53" s="3" t="s">
+        <v>549</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>15</v>
@@ -3948,13 +4047,13 @@
         <v>957227395</v>
       </c>
       <c r="J53" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3962,7 +4061,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>20</v>
@@ -3976,7 +4075,7 @@
       <c r="F54" s="1">
         <v>10411240113</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G54" s="3">
         <v>41124011</v>
       </c>
       <c r="H54" s="1" t="s">
@@ -3986,10 +4085,10 @@
         <v>982240470</v>
       </c>
       <c r="J54" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="L54" s="1"/>
     </row>
@@ -3998,7 +4097,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>13</v>
@@ -4012,8 +4111,8 @@
       <c r="F55" s="1">
         <v>10096106985</v>
       </c>
-      <c r="G55" s="1">
-        <v>9610698</v>
+      <c r="G55" s="3" t="s">
+        <v>552</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>15</v>
@@ -4022,13 +4121,13 @@
         <v>956251601</v>
       </c>
       <c r="J55" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="L55" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -4036,13 +4135,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E56" s="1">
         <v>40</v>
@@ -4050,7 +4149,7 @@
       <c r="F56" s="1">
         <v>10407698776</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G56" s="3">
         <v>40769877</v>
       </c>
       <c r="H56" s="1" t="s">
@@ -4060,13 +4159,13 @@
         <v>968880190</v>
       </c>
       <c r="J56" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="L56" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -4074,13 +4173,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E57" s="1">
         <v>40</v>
@@ -4088,8 +4187,8 @@
       <c r="F57" s="1">
         <v>10096779238</v>
       </c>
-      <c r="G57" s="1">
-        <v>9677923</v>
+      <c r="G57" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>15</v>
@@ -4098,13 +4197,13 @@
         <v>990281281</v>
       </c>
       <c r="J57" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="L57" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -4112,7 +4211,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>13</v>
@@ -4126,7 +4225,7 @@
       <c r="F58" s="1">
         <v>10469415428</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58" s="3">
         <v>46941542</v>
       </c>
       <c r="H58" s="1" t="s">
@@ -4136,13 +4235,13 @@
         <v>987852129</v>
       </c>
       <c r="J58" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="L58" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -4150,13 +4249,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E59" s="1">
         <v>40</v>
@@ -4164,7 +4263,7 @@
       <c r="F59" s="1">
         <v>10417999928</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" s="3">
         <v>41799992</v>
       </c>
       <c r="H59" s="1" t="s">
@@ -4174,13 +4273,13 @@
         <v>942054809</v>
       </c>
       <c r="J59" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="L59" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -4188,13 +4287,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E60" s="1">
         <v>40</v>
@@ -4202,7 +4301,7 @@
       <c r="F60" s="1">
         <v>10736875191</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G60" s="3">
         <v>73687519</v>
       </c>
       <c r="H60" s="1" t="s">
@@ -4212,13 +4311,13 @@
         <v>14078678551</v>
       </c>
       <c r="J60" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="L60" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -4226,7 +4325,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>13</v>
@@ -4240,7 +4339,7 @@
       <c r="F61" s="1">
         <v>10201171275</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G61" s="3">
         <v>20117127</v>
       </c>
       <c r="H61" s="1" t="s">
@@ -4250,13 +4349,13 @@
         <v>997041711</v>
       </c>
       <c r="J61" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="L61" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -4264,13 +4363,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E62" s="1">
         <v>40</v>
@@ -4278,7 +4377,7 @@
       <c r="F62" s="1">
         <v>10402159664</v>
       </c>
-      <c r="G62" s="1">
+      <c r="G62" s="3">
         <v>40215966</v>
       </c>
       <c r="H62" s="1" t="s">
@@ -4288,13 +4387,13 @@
         <v>950707772</v>
       </c>
       <c r="J62" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="L62" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -4302,7 +4401,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>13</v>
@@ -4316,7 +4415,7 @@
       <c r="F63" s="1">
         <v>10740269211</v>
       </c>
-      <c r="G63" s="1">
+      <c r="G63" s="3">
         <v>74026921</v>
       </c>
       <c r="H63" s="1" t="s">
@@ -4326,13 +4425,13 @@
         <v>958248948</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="L63" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -4340,13 +4439,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E64" s="1">
         <v>40</v>
@@ -4354,7 +4453,7 @@
       <c r="F64" s="1">
         <v>10409430428</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G64" s="3">
         <v>40943042</v>
       </c>
       <c r="H64" s="1" t="s">
@@ -4364,13 +4463,13 @@
         <v>970724595</v>
       </c>
       <c r="J64" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K64" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="L64" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -4378,7 +4477,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>13</v>
@@ -4392,7 +4491,7 @@
       <c r="F65" s="1">
         <v>10701516147</v>
       </c>
-      <c r="G65" s="1">
+      <c r="G65" s="3">
         <v>70151614</v>
       </c>
       <c r="H65" s="1" t="s">
@@ -4402,13 +4501,13 @@
         <v>989468400</v>
       </c>
       <c r="J65" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="L65" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -4416,7 +4515,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>13</v>
@@ -4430,7 +4529,7 @@
       <c r="F66" s="1">
         <v>10255408530</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G66" s="3">
         <v>25540853</v>
       </c>
       <c r="H66" s="1" t="s">
@@ -4440,13 +4539,13 @@
         <v>983330076</v>
       </c>
       <c r="J66" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="L66" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -4454,7 +4553,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>13</v>
@@ -4468,8 +4567,8 @@
       <c r="F67" s="1">
         <v>10040837324</v>
       </c>
-      <c r="G67" s="1">
-        <v>4083732</v>
+      <c r="G67" s="3" t="s">
+        <v>522</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>15</v>
@@ -4478,10 +4577,10 @@
         <v>963959088</v>
       </c>
       <c r="J67" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="L67" s="1"/>
     </row>
@@ -4490,7 +4589,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>13</v>
@@ -4504,7 +4603,7 @@
       <c r="F68" s="1">
         <v>10403008490</v>
       </c>
-      <c r="G68" s="1">
+      <c r="G68" s="3">
         <v>40300849</v>
       </c>
       <c r="H68" s="1" t="s">
@@ -4514,13 +4613,13 @@
         <v>990381690</v>
       </c>
       <c r="J68" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L68" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -4528,7 +4627,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>13</v>
@@ -4542,7 +4641,7 @@
       <c r="F69" s="1">
         <v>10101613360</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G69" s="3">
         <v>10161336</v>
       </c>
       <c r="H69" s="1" t="s">
@@ -4552,13 +4651,13 @@
         <v>986955266</v>
       </c>
       <c r="J69" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="L69" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -4566,7 +4665,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>13</v>
@@ -4580,7 +4679,7 @@
       <c r="F70" s="1">
         <v>10479740661</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G70" s="3">
         <v>47974066</v>
       </c>
       <c r="H70" s="1" t="s">
@@ -4590,13 +4689,13 @@
         <v>973581715</v>
       </c>
       <c r="J70" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -4604,7 +4703,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>13</v>
@@ -4618,7 +4717,7 @@
       <c r="F71" s="1">
         <v>1047974066</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G71" s="3">
         <v>47974066</v>
       </c>
       <c r="H71" s="1" t="s">
@@ -4628,13 +4727,13 @@
         <v>973581715</v>
       </c>
       <c r="J71" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="L71" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -4642,13 +4741,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E72" s="1">
         <v>40</v>
@@ -4656,7 +4755,7 @@
       <c r="F72" s="1">
         <v>10727671299</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G72" s="3">
         <v>72767129</v>
       </c>
       <c r="H72" s="1" t="s">
@@ -4666,13 +4765,13 @@
         <v>994978232</v>
       </c>
       <c r="J72" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="K72" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="L72" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -4680,7 +4779,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>13</v>
@@ -4694,7 +4793,7 @@
       <c r="F73" s="1">
         <v>10705708008</v>
       </c>
-      <c r="G73" s="1">
+      <c r="G73" s="3">
         <v>70570800</v>
       </c>
       <c r="H73" s="1" t="s">
@@ -4704,13 +4803,13 @@
         <v>941108612</v>
       </c>
       <c r="J73" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="L73" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -4718,7 +4817,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>13</v>
@@ -4732,7 +4831,7 @@
       <c r="F74" s="1">
         <v>10100762019</v>
       </c>
-      <c r="G74" s="1">
+      <c r="G74" s="3">
         <v>10076201</v>
       </c>
       <c r="H74" s="1" t="s">
@@ -4742,13 +4841,13 @@
         <v>999973262</v>
       </c>
       <c r="J74" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -4756,7 +4855,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>13</v>
@@ -4770,7 +4869,7 @@
       <c r="F75" s="1">
         <v>10464490553</v>
       </c>
-      <c r="G75" s="1">
+      <c r="G75" s="3">
         <v>46449055</v>
       </c>
       <c r="H75" s="1" t="s">
@@ -4780,13 +4879,13 @@
         <v>910017343</v>
       </c>
       <c r="J75" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K75" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="L75" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -4794,7 +4893,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>13</v>
@@ -4808,7 +4907,7 @@
       <c r="F76" s="1">
         <v>10433109789</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G76" s="3">
         <v>43310978</v>
       </c>
       <c r="H76" s="1" t="s">
@@ -4818,13 +4917,13 @@
         <v>999417514</v>
       </c>
       <c r="J76" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="L76" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -4832,7 +4931,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>13</v>
@@ -4846,8 +4945,8 @@
       <c r="F77" s="1">
         <v>10093423521</v>
       </c>
-      <c r="G77" s="1">
-        <v>9342352</v>
+      <c r="G77" s="3" t="s">
+        <v>546</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>15</v>
@@ -4856,13 +4955,13 @@
         <v>999732000</v>
       </c>
       <c r="J77" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K77" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="L77" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4870,7 +4969,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>13</v>
@@ -4884,7 +4983,7 @@
       <c r="F78" s="1">
         <v>10406512091</v>
       </c>
-      <c r="G78" s="1">
+      <c r="G78" s="3">
         <v>40651209</v>
       </c>
       <c r="H78" s="1" t="s">
@@ -4894,13 +4993,13 @@
         <v>958585564</v>
       </c>
       <c r="J78" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="K78" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="L78" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4908,7 +5007,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>13</v>
@@ -4922,7 +5021,7 @@
       <c r="F79" s="1">
         <v>10723944720</v>
       </c>
-      <c r="G79" s="1">
+      <c r="G79" s="3">
         <v>72394472</v>
       </c>
       <c r="H79" s="1" t="s">
@@ -4932,13 +5031,13 @@
         <v>931796931</v>
       </c>
       <c r="J79" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="L79" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4946,13 +5045,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E80" s="1">
         <v>40</v>
@@ -4960,8 +5059,8 @@
       <c r="F80" s="1">
         <v>10098884110</v>
       </c>
-      <c r="G80" s="1">
-        <v>9888411</v>
+      <c r="G80" s="3" t="s">
+        <v>555</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>26</v>
@@ -4976,7 +5075,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>13</v>
@@ -4990,8 +5089,8 @@
       <c r="F81" s="1">
         <v>10080086101</v>
       </c>
-      <c r="G81" s="1">
-        <v>8008610</v>
+      <c r="G81" s="3" t="s">
+        <v>538</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>26</v>
@@ -5000,13 +5099,13 @@
         <v>989339707</v>
       </c>
       <c r="J81" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="K81" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="L81" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -5014,7 +5113,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>13</v>
@@ -5028,7 +5127,7 @@
       <c r="F82" s="1">
         <v>10457166601</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G82" s="3">
         <v>45716660</v>
       </c>
       <c r="H82" s="1" t="s">
@@ -5038,13 +5137,13 @@
         <v>980860556</v>
       </c>
       <c r="J82" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="K82" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="L82" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -5052,7 +5151,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>13</v>
@@ -5066,7 +5165,7 @@
       <c r="F83" s="1">
         <v>10257820080</v>
       </c>
-      <c r="G83" s="1">
+      <c r="G83" s="3">
         <v>25782008</v>
       </c>
       <c r="H83" s="1" t="s">
@@ -5076,13 +5175,13 @@
         <v>997152497</v>
       </c>
       <c r="J83" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K83" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="L83" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -5090,7 +5189,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>13</v>
@@ -5104,7 +5203,7 @@
       <c r="F84" s="1">
         <v>10471350431</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G84" s="3">
         <v>47135043</v>
       </c>
       <c r="H84" s="1" t="s">
@@ -5114,10 +5213,10 @@
         <v>957776581</v>
       </c>
       <c r="J84" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="K84" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="L84" s="1"/>
     </row>
@@ -5126,7 +5225,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>13</v>
@@ -5140,7 +5239,7 @@
       <c r="F85" s="1">
         <v>10455790005</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G85" s="3">
         <v>45579000</v>
       </c>
       <c r="H85" s="1" t="s">
@@ -5150,13 +5249,13 @@
         <v>982088063</v>
       </c>
       <c r="J85" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="K85" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="L85" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -5164,7 +5263,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>13</v>
@@ -5178,7 +5277,7 @@
       <c r="F86" s="1">
         <v>10432590815</v>
       </c>
-      <c r="G86" s="1">
+      <c r="G86" s="3">
         <v>43259081</v>
       </c>
       <c r="H86" s="1" t="s">
@@ -5188,13 +5287,13 @@
         <v>997021475</v>
       </c>
       <c r="J86" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="L86" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -5202,7 +5301,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>13</v>
@@ -5216,8 +5315,8 @@
       <c r="F87" s="1">
         <v>10067000132</v>
       </c>
-      <c r="G87" s="1">
-        <v>6700013</v>
+      <c r="G87" s="3" t="s">
+        <v>526</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>26</v>
@@ -5226,13 +5325,13 @@
         <v>943910216</v>
       </c>
       <c r="J87" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="K87" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="L87" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -5240,7 +5339,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>13</v>
@@ -5254,7 +5353,7 @@
       <c r="F88" s="1">
         <v>10713759941</v>
       </c>
-      <c r="G88" s="1">
+      <c r="G88" s="3">
         <v>71375994</v>
       </c>
       <c r="H88" s="1" t="s">
@@ -5264,13 +5363,13 @@
         <v>991571012</v>
       </c>
       <c r="J88" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="L88" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="L88" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -5278,13 +5377,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E89" s="1">
         <v>40</v>
@@ -5292,8 +5391,8 @@
       <c r="F89" s="1">
         <v>10095890241</v>
       </c>
-      <c r="G89" s="1">
-        <v>9589024</v>
+      <c r="G89" s="3" t="s">
+        <v>551</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>26</v>
@@ -5302,13 +5401,13 @@
         <v>997495164</v>
       </c>
       <c r="J89" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K89" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="L89" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -5316,7 +5415,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>13</v>
@@ -5330,7 +5429,7 @@
       <c r="F90" s="1">
         <v>10707654380</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G90" s="3">
         <v>70765438</v>
       </c>
       <c r="H90" s="1" t="s">
@@ -5340,13 +5439,13 @@
         <v>971535025</v>
       </c>
       <c r="J90" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="K90" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="L90" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -5354,13 +5453,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E91" s="1">
         <v>40</v>
@@ -5368,8 +5467,8 @@
       <c r="F91" s="1">
         <v>10064190089</v>
       </c>
-      <c r="G91" s="1">
-        <v>6419008</v>
+      <c r="G91" s="3" t="s">
+        <v>524</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>26</v>
@@ -5378,13 +5477,13 @@
         <v>987446505</v>
       </c>
       <c r="J91" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="K91" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="L91" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -5392,7 +5491,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>13</v>
@@ -5406,8 +5505,8 @@
       <c r="F92" s="1">
         <v>10094151398</v>
       </c>
-      <c r="G92" s="1">
-        <v>9415139</v>
+      <c r="G92" s="3" t="s">
+        <v>548</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>26</v>
@@ -5416,13 +5515,13 @@
         <v>989465081</v>
       </c>
       <c r="J92" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="L92" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -5430,7 +5529,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>13</v>
@@ -5444,8 +5543,8 @@
       <c r="F93" s="1">
         <v>10066760940</v>
       </c>
-      <c r="G93" s="1">
-        <v>6676094</v>
+      <c r="G93" s="3" t="s">
+        <v>525</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>26</v>
@@ -5454,13 +5553,13 @@
         <v>920590254</v>
       </c>
       <c r="J93" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="K93" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="L93" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -5468,7 +5567,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>13</v>
@@ -5482,7 +5581,7 @@
       <c r="F94" s="1">
         <v>10775406611</v>
       </c>
-      <c r="G94" s="1">
+      <c r="G94" s="3">
         <v>77540661</v>
       </c>
       <c r="H94" s="1" t="s">
@@ -5492,13 +5591,13 @@
         <v>971406002</v>
       </c>
       <c r="J94" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="L94" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -5506,7 +5605,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>20</v>
@@ -5520,8 +5619,8 @@
       <c r="F95" s="1">
         <v>10073503111</v>
       </c>
-      <c r="G95" s="1">
-        <v>7350311</v>
+      <c r="G95" s="3" t="s">
+        <v>530</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>15</v>
@@ -5530,13 +5629,13 @@
         <v>962986188</v>
       </c>
       <c r="J95" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="K95" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="K95" s="1" t="s">
+      <c r="L95" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -5544,13 +5643,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E96" s="1">
         <v>40</v>
@@ -5558,7 +5657,7 @@
       <c r="F96" s="1">
         <v>10412760277</v>
       </c>
-      <c r="G96" s="1">
+      <c r="G96" s="3">
         <v>41276027</v>
       </c>
       <c r="H96" s="1" t="s">
@@ -5568,10 +5667,10 @@
         <v>991838005</v>
       </c>
       <c r="J96" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="K96" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="L96" s="1"/>
     </row>
@@ -5580,7 +5679,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>13</v>
@@ -5594,23 +5693,23 @@
       <c r="F97" s="1">
         <v>10726592191</v>
       </c>
-      <c r="G97" s="1">
+      <c r="G97" s="3">
         <v>72659219</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="I97" s="1">
+        <v>959222749</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="K97" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="J97" s="1" t="s">
+      <c r="L97" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -5618,7 +5717,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>13</v>
@@ -5632,23 +5731,23 @@
       <c r="F98" s="1">
         <v>10724812584</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G98" s="3">
         <v>72481258</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="I98" s="1">
+        <v>928085619</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="L98" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -5656,7 +5755,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>20</v>
@@ -5670,7 +5769,7 @@
       <c r="F99" s="1">
         <v>10257688459</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G99" s="3">
         <v>25768845</v>
       </c>
       <c r="H99" s="1" t="s">
@@ -5680,10 +5779,10 @@
         <v>955674055</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="L99" s="1"/>
     </row>
@@ -5692,13 +5791,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E100" s="1">
         <v>40</v>
@@ -5706,7 +5805,7 @@
       <c r="F100" s="1">
         <v>10428113611</v>
       </c>
-      <c r="G100" s="1">
+      <c r="G100" s="3">
         <v>42811361</v>
       </c>
       <c r="H100" s="1" t="s">
@@ -5716,13 +5815,13 @@
         <v>980686737</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -5730,7 +5829,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>13</v>
@@ -5744,7 +5843,7 @@
       <c r="F101" s="1">
         <v>10427606525</v>
       </c>
-      <c r="G101" s="1">
+      <c r="G101" s="3">
         <v>42760652</v>
       </c>
       <c r="H101" s="1" t="s">
@@ -5754,13 +5853,13 @@
         <v>994618216</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -5768,7 +5867,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>13</v>
@@ -5782,7 +5881,7 @@
       <c r="F102" s="1">
         <v>10102030490</v>
       </c>
-      <c r="G102" s="1">
+      <c r="G102" s="3">
         <v>10203049</v>
       </c>
       <c r="H102" s="1" t="s">
@@ -5792,13 +5891,13 @@
         <v>999914518</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -5806,7 +5905,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>20</v>
@@ -5820,7 +5919,7 @@
       <c r="F103" s="1">
         <v>10458160509</v>
       </c>
-      <c r="G103" s="1">
+      <c r="G103" s="3">
         <v>45816050</v>
       </c>
       <c r="H103" s="1" t="s">
@@ -5836,13 +5935,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E104" s="1">
         <v>40</v>
@@ -5850,7 +5949,7 @@
       <c r="F104" s="1">
         <v>10729533039</v>
       </c>
-      <c r="G104" s="1">
+      <c r="G104" s="3">
         <v>72953303</v>
       </c>
       <c r="H104" s="1" t="s">
@@ -5860,13 +5959,13 @@
         <v>927877873</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5874,7 +5973,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>13</v>
@@ -5888,8 +5987,8 @@
       <c r="F105" s="1">
         <v>10086856714</v>
       </c>
-      <c r="G105" s="1">
-        <v>8685671</v>
+      <c r="G105" s="3" t="s">
+        <v>543</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>26</v>
@@ -5898,13 +5997,13 @@
         <v>954991073</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5912,7 +6011,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>13</v>
@@ -5926,7 +6025,7 @@
       <c r="F106" s="1">
         <v>10419998538</v>
       </c>
-      <c r="G106" s="1">
+      <c r="G106" s="3">
         <v>41999853</v>
       </c>
       <c r="H106" s="1" t="s">
@@ -5936,10 +6035,10 @@
         <v>993115346</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L106" s="1">
         <v>99</v>
@@ -5950,7 +6049,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>13</v>
@@ -5964,7 +6063,7 @@
       <c r="F107" s="1">
         <v>10754438091</v>
       </c>
-      <c r="G107" s="1">
+      <c r="G107" s="3">
         <v>75443809</v>
       </c>
       <c r="H107" s="1" t="s">
@@ -5974,13 +6073,13 @@
         <v>959978099</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5988,7 +6087,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>13</v>
@@ -6002,7 +6101,7 @@
       <c r="F108" s="1">
         <v>10428542181</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G108" s="3">
         <v>42854218</v>
       </c>
       <c r="H108" s="1" t="s">
@@ -6012,13 +6111,13 @@
         <v>997478572</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -6026,13 +6125,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E109" s="1">
         <v>40</v>
@@ -6040,8 +6139,8 @@
       <c r="F109" s="1">
         <v>10088345482</v>
       </c>
-      <c r="G109" s="1">
-        <v>8834548</v>
+      <c r="G109" s="3" t="s">
+        <v>544</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>15</v>
@@ -6050,13 +6149,13 @@
         <v>998802440</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -6064,7 +6163,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>13</v>
@@ -6078,23 +6177,23 @@
       <c r="F110" s="1">
         <v>10060173244</v>
       </c>
-      <c r="G110" s="1">
-        <v>6017324</v>
+      <c r="G110" s="3" t="s">
+        <v>523</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I110" s="1" t="s">
-        <v>425</v>
+      <c r="I110" s="1">
+        <v>969338549</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -6102,7 +6201,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>13</v>
@@ -6116,7 +6215,7 @@
       <c r="F111" s="1">
         <v>15601491891</v>
       </c>
-      <c r="G111" s="1">
+      <c r="G111" s="3">
         <v>60149189</v>
       </c>
       <c r="H111" s="1" t="s">
@@ -6126,13 +6225,13 @@
         <v>991879414</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -6140,7 +6239,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>13</v>
@@ -6154,8 +6253,8 @@
       <c r="F112" s="1">
         <v>10077308798</v>
       </c>
-      <c r="G112" s="1">
-        <v>7730879</v>
+      <c r="G112" s="3" t="s">
+        <v>536</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>26</v>
@@ -6164,13 +6263,13 @@
         <v>977619341</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -6178,13 +6277,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E113" s="1">
         <v>40</v>
@@ -6192,7 +6291,7 @@
       <c r="F113" s="1">
         <v>10413751573</v>
       </c>
-      <c r="G113" s="1">
+      <c r="G113" s="3">
         <v>41375157</v>
       </c>
       <c r="H113" s="1" t="s">
@@ -6202,13 +6301,13 @@
         <v>929478486</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -6216,7 +6315,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>13</v>
@@ -6230,7 +6329,7 @@
       <c r="F114" s="1">
         <v>10419691769</v>
       </c>
-      <c r="G114" s="1">
+      <c r="G114" s="3">
         <v>41969176</v>
       </c>
       <c r="H114" s="1" t="s">
@@ -6240,13 +6339,13 @@
         <v>931506673</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -6254,7 +6353,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>13</v>
@@ -6268,7 +6367,7 @@
       <c r="F115" s="1">
         <v>10473314016</v>
       </c>
-      <c r="G115" s="1">
+      <c r="G115" s="3">
         <v>47331401</v>
       </c>
       <c r="H115" s="1" t="s">
@@ -6278,13 +6377,13 @@
         <v>915352889</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -6292,7 +6391,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>13</v>
@@ -6306,8 +6405,8 @@
       <c r="F116" s="1">
         <v>10085637431</v>
       </c>
-      <c r="G116" s="1">
-        <v>8563743</v>
+      <c r="G116" s="3" t="s">
+        <v>542</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>26</v>
@@ -6316,13 +6415,13 @@
         <v>985182809</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -6330,7 +6429,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>20</v>
@@ -6344,8 +6443,8 @@
       <c r="F117" s="1">
         <v>10074516501</v>
       </c>
-      <c r="G117" s="1">
-        <v>7451650</v>
+      <c r="G117" s="3" t="s">
+        <v>531</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>15</v>
@@ -6354,13 +6453,13 @@
         <v>996436350</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -6368,7 +6467,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>13</v>
@@ -6382,7 +6481,7 @@
       <c r="F118" s="1">
         <v>10477227606</v>
       </c>
-      <c r="G118" s="1">
+      <c r="G118" s="3">
         <v>47722760</v>
       </c>
       <c r="H118" s="1" t="s">
@@ -6392,13 +6491,13 @@
         <v>966714417</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -6406,7 +6505,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>13</v>
@@ -6420,7 +6519,7 @@
       <c r="F119" s="1">
         <v>10412953229</v>
       </c>
-      <c r="G119" s="1">
+      <c r="G119" s="3">
         <v>41295322</v>
       </c>
       <c r="H119" s="1" t="s">
@@ -6430,13 +6529,13 @@
         <v>968779616</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -6444,7 +6543,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>20</v>
@@ -6458,7 +6557,7 @@
       <c r="F120" s="1">
         <v>10730336158</v>
       </c>
-      <c r="G120" s="1">
+      <c r="G120" s="3">
         <v>73033615</v>
       </c>
       <c r="H120" s="1" t="s">
@@ -6468,13 +6567,13 @@
         <v>933906283</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -6482,13 +6581,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E121" s="1">
         <v>40</v>
@@ -6496,7 +6595,7 @@
       <c r="F121" s="1">
         <v>10457605591</v>
       </c>
-      <c r="G121" s="1">
+      <c r="G121" s="3">
         <v>45760559</v>
       </c>
       <c r="H121" s="1" t="s">
@@ -6506,13 +6605,13 @@
         <v>970703283</v>
       </c>
       <c r="J121" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="K121" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="K121" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="L121" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -6520,13 +6619,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E122" s="1">
         <v>40</v>
@@ -6534,7 +6633,7 @@
       <c r="F122" s="1">
         <v>10106168712</v>
       </c>
-      <c r="G122" s="1">
+      <c r="G122" s="3">
         <v>10616871</v>
       </c>
       <c r="H122" s="1" t="s">
@@ -6544,13 +6643,13 @@
         <v>989354789</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -6558,7 +6657,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>13</v>
@@ -6572,8 +6671,8 @@
       <c r="F123" s="1">
         <v>10073491938</v>
       </c>
-      <c r="G123" s="1">
-        <v>7349193</v>
+      <c r="G123" s="3" t="s">
+        <v>529</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>15</v>
@@ -6582,13 +6681,13 @@
         <v>997608048</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -6596,7 +6695,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>20</v>
@@ -6610,7 +6709,7 @@
       <c r="F124" s="1">
         <v>10426927077</v>
       </c>
-      <c r="G124" s="1">
+      <c r="G124" s="3">
         <v>42692707</v>
       </c>
       <c r="H124" s="1" t="s">
@@ -6620,10 +6719,10 @@
         <v>986114573</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="L124" s="1"/>
     </row>
@@ -6632,7 +6731,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>13</v>
@@ -6646,7 +6745,7 @@
       <c r="F125" s="1">
         <v>10441323668</v>
       </c>
-      <c r="G125" s="1">
+      <c r="G125" s="3">
         <v>44132366</v>
       </c>
       <c r="H125" s="1" t="s">
@@ -6656,13 +6755,13 @@
         <v>961814417</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -6670,7 +6769,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>13</v>
@@ -6684,7 +6783,7 @@
       <c r="F126" s="1">
         <v>10256193111</v>
       </c>
-      <c r="G126" s="1">
+      <c r="G126" s="3">
         <v>25619311</v>
       </c>
       <c r="H126" s="1" t="s">
@@ -6694,13 +6793,13 @@
         <v>974971699</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -6708,7 +6807,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>13</v>
@@ -6722,7 +6821,7 @@
       <c r="F127" s="1">
         <v>10106515340</v>
       </c>
-      <c r="G127" s="1">
+      <c r="G127" s="3">
         <v>10651534</v>
       </c>
       <c r="H127" s="1" t="s">
@@ -6738,13 +6837,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E128" s="1">
         <v>40</v>
@@ -6752,7 +6851,7 @@
       <c r="F128" s="1">
         <v>10474902850</v>
       </c>
-      <c r="G128" s="1">
+      <c r="G128" s="3">
         <v>47490285</v>
       </c>
       <c r="H128" s="1" t="s">
@@ -6762,13 +6861,13 @@
         <v>960745470</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -6776,7 +6875,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>13</v>
@@ -6790,7 +6889,7 @@
       <c r="F129" s="1">
         <v>10449450596</v>
       </c>
-      <c r="G129" s="1">
+      <c r="G129" s="3">
         <v>44945059</v>
       </c>
       <c r="H129" s="1" t="s">
@@ -6800,13 +6899,13 @@
         <v>992951156</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -6814,7 +6913,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>20</v>
@@ -6828,8 +6927,8 @@
       <c r="F130" s="1">
         <v>10097771125</v>
       </c>
-      <c r="G130" s="1">
-        <v>9777112</v>
+      <c r="G130" s="3" t="s">
+        <v>554</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>15</v>
@@ -6838,13 +6937,13 @@
         <v>993299903</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -6852,7 +6951,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>13</v>
@@ -6866,7 +6965,7 @@
       <c r="F131" s="1">
         <v>10453680512</v>
       </c>
-      <c r="G131" s="1">
+      <c r="G131" s="3">
         <v>45368051</v>
       </c>
       <c r="H131" s="1" t="s">
@@ -6876,13 +6975,13 @@
         <v>956876507</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -6890,7 +6989,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>20</v>
@@ -6904,7 +7003,7 @@
       <c r="F132" s="1">
         <v>10104376679</v>
       </c>
-      <c r="G132" s="1">
+      <c r="G132" s="3">
         <v>10437667</v>
       </c>
       <c r="H132" s="1" t="s">
@@ -6914,10 +7013,10 @@
         <v>933453404</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="L132" s="1"/>
     </row>
@@ -6926,7 +7025,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>13</v>
@@ -6940,7 +7039,7 @@
       <c r="F133" s="1">
         <v>10428719668</v>
       </c>
-      <c r="G133" s="1">
+      <c r="G133" s="3">
         <v>42871966</v>
       </c>
       <c r="H133" s="1" t="s">
@@ -6950,13 +7049,13 @@
         <v>922650419</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -6964,7 +7063,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>13</v>
@@ -6978,8 +7077,8 @@
       <c r="F134" s="1">
         <v>10080504549</v>
       </c>
-      <c r="G134" s="1">
-        <v>8050454</v>
+      <c r="G134" s="3" t="s">
+        <v>539</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>26</v>
@@ -6988,13 +7087,13 @@
         <v>993462293</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -7002,7 +7101,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>13</v>
@@ -7016,7 +7115,7 @@
       <c r="F135" s="1">
         <v>10734422199</v>
       </c>
-      <c r="G135" s="1">
+      <c r="G135" s="3">
         <v>73442219</v>
       </c>
       <c r="H135" s="1" t="s">
@@ -7026,17 +7125,21 @@
         <v>955229427</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L135" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L135" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L135">
+      <sortCondition ref="B1:B135"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>